--- a/docs/bobot_kesulitan_modul_fprs_v3.xlsx
+++ b/docs/bobot_kesulitan_modul_fprs_v3.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Source\Comsup\falcon\Prototype\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Semua Modul" sheetId="1" r:id="rId1"/>
@@ -12,7 +17,7 @@
     <sheet name="Timeline MOBILE" sheetId="3" r:id="rId3"/>
     <sheet name="Ringkasan" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -268,13 +273,13 @@
     <t>Timeline WEB | excl. weekend + libur nasional RI | 22 Jul – 30 Sept 2026 | v3: Canvassing take-out</t>
   </si>
   <si>
-    <t>Timeline MOBILE | excl. weekend + libur nasional RI | 22 Jul – 30 Nov 2026 | v3: +4 FALCON MERGER Oct–Nov</t>
+    <t>Timeline MOBILE | excl. weekend + libur nasional RI | 10 Agu 2026 – 17 Des 2026 | v3: reschedule start 2026-08-10 (+4 FALCON MERGER)</t>
   </si>
   <si>
     <t>Ringkasan Timeline &amp; Bobot (v3)</t>
   </si>
   <si>
-    <t>WEB dan MOBILE paralel (dev berbeda). Periode 22 Jul – 30 Nov 2026. Hari kerja = Senin–Jumat dikurangi libur nasional/cuti bersama RI (SKB 3 Menteri 2026). v3: hapus Canvassing (take-out); tambah 4 FALCON MERGER di ujung Mobile (setelah Sinkronisasi) sampai November.</t>
+    <t>WEB dan MOBILE paralel (dev berbeda). WEB: 22 Jul – 30 Sep 2026. MOBILE: 10 Agu 2026 – 17 Des 2026. Hari kerja = Senin–Jumat dikurangi libur nasional/cuti bersama RI (SKB 3 Menteri 2026). v3: hapus Canvassing (take-out); +4 FALCON MERGER; Mobile di-reschedule mulai 10 Agu 2026.</t>
   </si>
   <si>
     <t>Jumlah Modul</t>
@@ -331,7 +336,7 @@
     <t>3. Hanya hari kerja efektif: Senin–Jumat, minus libur nasional &amp; cuti bersama RI.</t>
   </si>
   <si>
-    <t>4. Track WEB: 22-Jul-2026 s/d 30-Sep-2026 (Canvassing dihapus di v3). Track MOBILE: 22-Jul-2026 s/d 30-Nov-2026 (+ FALCON MERGER setelah Sinkronisasi).</t>
+    <t>4. Track WEB: 22-Jul-2026 s/d 30-Sep-2026 (Canvassing dihapus di v3). Track MOBILE: 10 Agu 2026 s/d 17 Des 2026 (reschedule 2026-08-10; + FALCON MERGER setelah Sinkronisasi).</t>
   </si>
   <si>
     <t>5. Skala bobot: 1 ringan – 5 sangat berat. Target total bobot = 60 (WEB 24 + MOBILE 36). FALCON MERGER: Visit Plan 3, POA 3, Partner 2, Dashboard 2.</t>
@@ -462,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -500,9 +505,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -519,18 +521,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,13 +824,13 @@
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="1" max="1" width="6" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12" style="24" customWidth="1"/>
+    <col min="3" max="3" width="55" style="24" customWidth="1"/>
+    <col min="4" max="4" width="10" style="24" customWidth="1"/>
+    <col min="5" max="6" width="14" style="24" customWidth="1"/>
+    <col min="7" max="7" width="12" style="24" customWidth="1"/>
+    <col min="8" max="8" width="55" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.55" customHeight="1">
@@ -1148,11 +1158,11 @@
       <c r="D13" s="12">
         <v>1</v>
       </c>
-      <c r="E13" s="13">
-        <v>46225</v>
-      </c>
-      <c r="F13" s="13">
-        <v>46227</v>
+      <c r="E13" s="25">
+        <v>46244</v>
+      </c>
+      <c r="F13" s="25">
+        <v>46246</v>
       </c>
       <c r="G13" s="10">
         <v>3</v>
@@ -1174,11 +1184,11 @@
       <c r="D14" s="12">
         <v>1</v>
       </c>
-      <c r="E14" s="13">
-        <v>46230</v>
-      </c>
-      <c r="F14" s="13">
-        <v>46232</v>
+      <c r="E14" s="25">
+        <v>46247</v>
+      </c>
+      <c r="F14" s="25">
+        <v>46252</v>
       </c>
       <c r="G14" s="10">
         <v>3</v>
@@ -1200,11 +1210,11 @@
       <c r="D15" s="12">
         <v>1</v>
       </c>
-      <c r="E15" s="13">
-        <v>46233</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46233</v>
+      <c r="E15" s="25">
+        <v>46253</v>
+      </c>
+      <c r="F15" s="25">
+        <v>46253</v>
       </c>
       <c r="G15" s="10">
         <v>1</v>
@@ -1226,11 +1236,11 @@
       <c r="D16" s="12">
         <v>1</v>
       </c>
-      <c r="E16" s="13">
-        <v>46234</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46234</v>
+      <c r="E16" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F16" s="25">
+        <v>46254</v>
       </c>
       <c r="G16" s="10">
         <v>1</v>
@@ -1252,11 +1262,11 @@
       <c r="D17" s="12">
         <v>1</v>
       </c>
-      <c r="E17" s="13">
-        <v>46237</v>
-      </c>
-      <c r="F17" s="13">
-        <v>46239</v>
+      <c r="E17" s="25">
+        <v>46255</v>
+      </c>
+      <c r="F17" s="25">
+        <v>46260</v>
       </c>
       <c r="G17" s="10">
         <v>3</v>
@@ -1278,11 +1288,11 @@
       <c r="D18" s="12">
         <v>3</v>
       </c>
-      <c r="E18" s="13">
-        <v>46240</v>
-      </c>
-      <c r="F18" s="13">
-        <v>46246</v>
+      <c r="E18" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F18" s="25">
+        <v>46267</v>
       </c>
       <c r="G18" s="10">
         <v>5</v>
@@ -1304,11 +1314,11 @@
       <c r="D19" s="12">
         <v>1</v>
       </c>
-      <c r="E19" s="13">
-        <v>46247</v>
-      </c>
-      <c r="F19" s="13">
-        <v>46252</v>
+      <c r="E19" s="25">
+        <v>46268</v>
+      </c>
+      <c r="F19" s="25">
+        <v>46272</v>
       </c>
       <c r="G19" s="10">
         <v>3</v>
@@ -1330,11 +1340,11 @@
       <c r="D20" s="12">
         <v>2</v>
       </c>
-      <c r="E20" s="13">
-        <v>46253</v>
-      </c>
-      <c r="F20" s="13">
-        <v>46258</v>
+      <c r="E20" s="25">
+        <v>46273</v>
+      </c>
+      <c r="F20" s="25">
+        <v>46276</v>
       </c>
       <c r="G20" s="10">
         <v>4</v>
@@ -1356,11 +1366,11 @@
       <c r="D21" s="12">
         <v>1</v>
       </c>
-      <c r="E21" s="13">
-        <v>46260</v>
-      </c>
-      <c r="F21" s="13">
-        <v>46262</v>
+      <c r="E21" s="25">
+        <v>46279</v>
+      </c>
+      <c r="F21" s="25">
+        <v>46281</v>
       </c>
       <c r="G21" s="10">
         <v>3</v>
@@ -1382,11 +1392,11 @@
       <c r="D22" s="12">
         <v>1</v>
       </c>
-      <c r="E22" s="13">
-        <v>46265</v>
-      </c>
-      <c r="F22" s="13">
-        <v>46265</v>
+      <c r="E22" s="25">
+        <v>46282</v>
+      </c>
+      <c r="F22" s="25">
+        <v>46282</v>
       </c>
       <c r="G22" s="10">
         <v>1</v>
@@ -1408,11 +1418,11 @@
       <c r="D23" s="12">
         <v>1</v>
       </c>
-      <c r="E23" s="13">
-        <v>46266</v>
-      </c>
-      <c r="F23" s="13">
-        <v>46266</v>
+      <c r="E23" s="25">
+        <v>46283</v>
+      </c>
+      <c r="F23" s="25">
+        <v>46283</v>
       </c>
       <c r="G23" s="10">
         <v>1</v>
@@ -1434,11 +1444,11 @@
       <c r="D24" s="12">
         <v>1</v>
       </c>
-      <c r="E24" s="13">
-        <v>46267</v>
-      </c>
-      <c r="F24" s="13">
-        <v>46269</v>
+      <c r="E24" s="25">
+        <v>46286</v>
+      </c>
+      <c r="F24" s="25">
+        <v>46288</v>
       </c>
       <c r="G24" s="10">
         <v>3</v>
@@ -1460,11 +1470,11 @@
       <c r="D25" s="12">
         <v>1</v>
       </c>
-      <c r="E25" s="13">
-        <v>46272</v>
-      </c>
-      <c r="F25" s="13">
-        <v>46274</v>
+      <c r="E25" s="25">
+        <v>46289</v>
+      </c>
+      <c r="F25" s="25">
+        <v>46293</v>
       </c>
       <c r="G25" s="10">
         <v>3</v>
@@ -1486,11 +1496,11 @@
       <c r="D26" s="12">
         <v>1</v>
       </c>
-      <c r="E26" s="13">
-        <v>46275</v>
-      </c>
-      <c r="F26" s="13">
-        <v>46275</v>
+      <c r="E26" s="25">
+        <v>46294</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46294</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -1512,11 +1522,11 @@
       <c r="D27" s="12">
         <v>1</v>
       </c>
-      <c r="E27" s="13">
-        <v>46276</v>
-      </c>
-      <c r="F27" s="13">
-        <v>46276</v>
+      <c r="E27" s="25">
+        <v>46295</v>
+      </c>
+      <c r="F27" s="25">
+        <v>46295</v>
       </c>
       <c r="G27" s="10">
         <v>1</v>
@@ -1538,11 +1548,11 @@
       <c r="D28" s="12">
         <v>1</v>
       </c>
-      <c r="E28" s="13">
-        <v>46279</v>
-      </c>
-      <c r="F28" s="13">
-        <v>46279</v>
+      <c r="E28" s="25">
+        <v>46296</v>
+      </c>
+      <c r="F28" s="25">
+        <v>46296</v>
       </c>
       <c r="G28" s="10">
         <v>1</v>
@@ -1564,11 +1574,11 @@
       <c r="D29" s="12">
         <v>2</v>
       </c>
-      <c r="E29" s="13">
-        <v>46280</v>
-      </c>
-      <c r="F29" s="13">
-        <v>46282</v>
+      <c r="E29" s="25">
+        <v>46297</v>
+      </c>
+      <c r="F29" s="25">
+        <v>46301</v>
       </c>
       <c r="G29" s="10">
         <v>3</v>
@@ -1590,11 +1600,11 @@
       <c r="D30" s="12">
         <v>2</v>
       </c>
-      <c r="E30" s="13">
-        <v>46283</v>
-      </c>
-      <c r="F30" s="13">
-        <v>46287</v>
+      <c r="E30" s="25">
+        <v>46302</v>
+      </c>
+      <c r="F30" s="25">
+        <v>46304</v>
       </c>
       <c r="G30" s="10">
         <v>3</v>
@@ -1616,11 +1626,11 @@
       <c r="D31" s="12">
         <v>2</v>
       </c>
-      <c r="E31" s="13">
-        <v>46288</v>
-      </c>
-      <c r="F31" s="13">
-        <v>46290</v>
+      <c r="E31" s="25">
+        <v>46307</v>
+      </c>
+      <c r="F31" s="25">
+        <v>46309</v>
       </c>
       <c r="G31" s="10">
         <v>3</v>
@@ -1642,11 +1652,11 @@
       <c r="D32" s="12">
         <v>1</v>
       </c>
-      <c r="E32" s="13">
-        <v>46293</v>
-      </c>
-      <c r="F32" s="13">
-        <v>46295</v>
+      <c r="E32" s="25">
+        <v>46310</v>
+      </c>
+      <c r="F32" s="25">
+        <v>46314</v>
       </c>
       <c r="G32" s="10">
         <v>3</v>
@@ -1668,11 +1678,11 @@
       <c r="D33" s="12">
         <v>3</v>
       </c>
-      <c r="E33" s="13">
-        <v>46296</v>
-      </c>
-      <c r="F33" s="13">
-        <v>46314</v>
+      <c r="E33" s="25">
+        <v>46315</v>
+      </c>
+      <c r="F33" s="25">
+        <v>46331</v>
       </c>
       <c r="G33" s="10">
         <v>13</v>
@@ -1694,11 +1704,11 @@
       <c r="D34" s="12">
         <v>3</v>
       </c>
-      <c r="E34" s="13">
-        <v>46315</v>
-      </c>
-      <c r="F34" s="13">
-        <v>46331</v>
+      <c r="E34" s="25">
+        <v>46332</v>
+      </c>
+      <c r="F34" s="25">
+        <v>46350</v>
       </c>
       <c r="G34" s="10">
         <v>13</v>
@@ -1720,11 +1730,11 @@
       <c r="D35" s="12">
         <v>2</v>
       </c>
-      <c r="E35" s="13">
-        <v>46332</v>
-      </c>
-      <c r="F35" s="13">
-        <v>46344</v>
+      <c r="E35" s="25">
+        <v>46351</v>
+      </c>
+      <c r="F35" s="25">
+        <v>46363</v>
       </c>
       <c r="G35" s="10">
         <v>9</v>
@@ -1746,11 +1756,11 @@
       <c r="D36" s="12">
         <v>2</v>
       </c>
-      <c r="E36" s="13">
-        <v>46345</v>
-      </c>
-      <c r="F36" s="13">
-        <v>46356</v>
+      <c r="E36" s="25">
+        <v>46364</v>
+      </c>
+      <c r="F36" s="25">
+        <v>46373</v>
       </c>
       <c r="G36" s="10">
         <v>8</v>
@@ -1759,25 +1769,25 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="43.2">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="15" t="s">
+    <row r="37" spans="1:8" ht="43.2" customHeight="1">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="13">
         <v>60</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="15">
         <v>46225</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="15">
         <v>46356</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="13">
         <v>135</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="16" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1792,13 +1802,13 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="1" max="1" width="6" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12" style="24" customWidth="1"/>
+    <col min="3" max="3" width="55" style="24" customWidth="1"/>
+    <col min="4" max="4" width="10" style="24" customWidth="1"/>
+    <col min="5" max="6" width="14" style="24" customWidth="1"/>
+    <col min="7" max="7" width="12" style="24" customWidth="1"/>
+    <col min="8" max="8" width="55" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.55" customHeight="1">
@@ -2113,25 +2123,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="28.8">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+    <row r="13" spans="1:8" ht="28.8" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>24</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>46225</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>46295</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>43</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2146,13 +2156,13 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="1" max="1" width="6" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12" style="24" customWidth="1"/>
+    <col min="3" max="3" width="55" style="24" customWidth="1"/>
+    <col min="4" max="4" width="10" style="24" customWidth="1"/>
+    <col min="5" max="6" width="14" style="24" customWidth="1"/>
+    <col min="7" max="7" width="12" style="24" customWidth="1"/>
+    <col min="8" max="8" width="55" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.55" customHeight="1">
@@ -2194,11 +2204,11 @@
       <c r="D2" s="12">
         <v>1</v>
       </c>
-      <c r="E2" s="13">
-        <v>46225</v>
-      </c>
-      <c r="F2" s="13">
-        <v>46227</v>
+      <c r="E2" s="25">
+        <v>46244</v>
+      </c>
+      <c r="F2" s="25">
+        <v>46246</v>
       </c>
       <c r="G2" s="10">
         <v>3</v>
@@ -2220,11 +2230,11 @@
       <c r="D3" s="12">
         <v>1</v>
       </c>
-      <c r="E3" s="13">
-        <v>46230</v>
-      </c>
-      <c r="F3" s="13">
-        <v>46232</v>
+      <c r="E3" s="25">
+        <v>46247</v>
+      </c>
+      <c r="F3" s="25">
+        <v>46252</v>
       </c>
       <c r="G3" s="10">
         <v>3</v>
@@ -2246,11 +2256,11 @@
       <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>46233</v>
-      </c>
-      <c r="F4" s="13">
-        <v>46233</v>
+      <c r="E4" s="25">
+        <v>46253</v>
+      </c>
+      <c r="F4" s="25">
+        <v>46253</v>
       </c>
       <c r="G4" s="10">
         <v>1</v>
@@ -2272,11 +2282,11 @@
       <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="13">
-        <v>46234</v>
-      </c>
-      <c r="F5" s="13">
-        <v>46234</v>
+      <c r="E5" s="25">
+        <v>46254</v>
+      </c>
+      <c r="F5" s="25">
+        <v>46254</v>
       </c>
       <c r="G5" s="10">
         <v>1</v>
@@ -2298,11 +2308,11 @@
       <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="13">
-        <v>46237</v>
-      </c>
-      <c r="F6" s="13">
-        <v>46239</v>
+      <c r="E6" s="25">
+        <v>46255</v>
+      </c>
+      <c r="F6" s="25">
+        <v>46260</v>
       </c>
       <c r="G6" s="10">
         <v>3</v>
@@ -2324,11 +2334,11 @@
       <c r="D7" s="12">
         <v>3</v>
       </c>
-      <c r="E7" s="13">
-        <v>46240</v>
-      </c>
-      <c r="F7" s="13">
-        <v>46246</v>
+      <c r="E7" s="25">
+        <v>46261</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46267</v>
       </c>
       <c r="G7" s="10">
         <v>5</v>
@@ -2350,11 +2360,11 @@
       <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E8" s="13">
-        <v>46247</v>
-      </c>
-      <c r="F8" s="13">
-        <v>46252</v>
+      <c r="E8" s="25">
+        <v>46268</v>
+      </c>
+      <c r="F8" s="25">
+        <v>46272</v>
       </c>
       <c r="G8" s="10">
         <v>3</v>
@@ -2376,11 +2386,11 @@
       <c r="D9" s="12">
         <v>2</v>
       </c>
-      <c r="E9" s="13">
-        <v>46253</v>
-      </c>
-      <c r="F9" s="13">
-        <v>46258</v>
+      <c r="E9" s="25">
+        <v>46273</v>
+      </c>
+      <c r="F9" s="25">
+        <v>46276</v>
       </c>
       <c r="G9" s="10">
         <v>4</v>
@@ -2402,11 +2412,11 @@
       <c r="D10" s="12">
         <v>1</v>
       </c>
-      <c r="E10" s="13">
-        <v>46260</v>
-      </c>
-      <c r="F10" s="13">
-        <v>46262</v>
+      <c r="E10" s="25">
+        <v>46279</v>
+      </c>
+      <c r="F10" s="25">
+        <v>46281</v>
       </c>
       <c r="G10" s="10">
         <v>3</v>
@@ -2428,11 +2438,11 @@
       <c r="D11" s="12">
         <v>1</v>
       </c>
-      <c r="E11" s="13">
-        <v>46265</v>
-      </c>
-      <c r="F11" s="13">
-        <v>46265</v>
+      <c r="E11" s="25">
+        <v>46282</v>
+      </c>
+      <c r="F11" s="25">
+        <v>46282</v>
       </c>
       <c r="G11" s="10">
         <v>1</v>
@@ -2454,11 +2464,11 @@
       <c r="D12" s="12">
         <v>1</v>
       </c>
-      <c r="E12" s="13">
-        <v>46266</v>
-      </c>
-      <c r="F12" s="13">
-        <v>46266</v>
+      <c r="E12" s="25">
+        <v>46283</v>
+      </c>
+      <c r="F12" s="25">
+        <v>46283</v>
       </c>
       <c r="G12" s="10">
         <v>1</v>
@@ -2480,11 +2490,11 @@
       <c r="D13" s="12">
         <v>1</v>
       </c>
-      <c r="E13" s="13">
-        <v>46267</v>
-      </c>
-      <c r="F13" s="13">
-        <v>46269</v>
+      <c r="E13" s="25">
+        <v>46286</v>
+      </c>
+      <c r="F13" s="25">
+        <v>46288</v>
       </c>
       <c r="G13" s="10">
         <v>3</v>
@@ -2506,11 +2516,11 @@
       <c r="D14" s="12">
         <v>1</v>
       </c>
-      <c r="E14" s="13">
-        <v>46272</v>
-      </c>
-      <c r="F14" s="13">
-        <v>46274</v>
+      <c r="E14" s="25">
+        <v>46289</v>
+      </c>
+      <c r="F14" s="25">
+        <v>46293</v>
       </c>
       <c r="G14" s="10">
         <v>3</v>
@@ -2532,11 +2542,11 @@
       <c r="D15" s="12">
         <v>1</v>
       </c>
-      <c r="E15" s="13">
-        <v>46275</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46275</v>
+      <c r="E15" s="25">
+        <v>46294</v>
+      </c>
+      <c r="F15" s="25">
+        <v>46294</v>
       </c>
       <c r="G15" s="10">
         <v>1</v>
@@ -2558,11 +2568,11 @@
       <c r="D16" s="12">
         <v>1</v>
       </c>
-      <c r="E16" s="13">
-        <v>46276</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46276</v>
+      <c r="E16" s="25">
+        <v>46295</v>
+      </c>
+      <c r="F16" s="25">
+        <v>46295</v>
       </c>
       <c r="G16" s="10">
         <v>1</v>
@@ -2584,11 +2594,11 @@
       <c r="D17" s="12">
         <v>1</v>
       </c>
-      <c r="E17" s="13">
-        <v>46279</v>
-      </c>
-      <c r="F17" s="13">
-        <v>46279</v>
+      <c r="E17" s="25">
+        <v>46296</v>
+      </c>
+      <c r="F17" s="25">
+        <v>46296</v>
       </c>
       <c r="G17" s="10">
         <v>1</v>
@@ -2610,11 +2620,11 @@
       <c r="D18" s="12">
         <v>2</v>
       </c>
-      <c r="E18" s="13">
-        <v>46280</v>
-      </c>
-      <c r="F18" s="13">
-        <v>46282</v>
+      <c r="E18" s="25">
+        <v>46297</v>
+      </c>
+      <c r="F18" s="25">
+        <v>46301</v>
       </c>
       <c r="G18" s="10">
         <v>3</v>
@@ -2636,11 +2646,11 @@
       <c r="D19" s="12">
         <v>2</v>
       </c>
-      <c r="E19" s="13">
-        <v>46283</v>
-      </c>
-      <c r="F19" s="13">
-        <v>46287</v>
+      <c r="E19" s="25">
+        <v>46302</v>
+      </c>
+      <c r="F19" s="25">
+        <v>46304</v>
       </c>
       <c r="G19" s="10">
         <v>3</v>
@@ -2662,11 +2672,11 @@
       <c r="D20" s="12">
         <v>2</v>
       </c>
-      <c r="E20" s="13">
-        <v>46288</v>
-      </c>
-      <c r="F20" s="13">
-        <v>46290</v>
+      <c r="E20" s="25">
+        <v>46307</v>
+      </c>
+      <c r="F20" s="25">
+        <v>46309</v>
       </c>
       <c r="G20" s="10">
         <v>3</v>
@@ -2688,11 +2698,11 @@
       <c r="D21" s="12">
         <v>1</v>
       </c>
-      <c r="E21" s="13">
-        <v>46293</v>
-      </c>
-      <c r="F21" s="13">
-        <v>46295</v>
+      <c r="E21" s="25">
+        <v>46310</v>
+      </c>
+      <c r="F21" s="25">
+        <v>46314</v>
       </c>
       <c r="G21" s="10">
         <v>3</v>
@@ -2714,11 +2724,11 @@
       <c r="D22" s="12">
         <v>3</v>
       </c>
-      <c r="E22" s="13">
-        <v>46296</v>
-      </c>
-      <c r="F22" s="13">
-        <v>46314</v>
+      <c r="E22" s="25">
+        <v>46315</v>
+      </c>
+      <c r="F22" s="25">
+        <v>46331</v>
       </c>
       <c r="G22" s="10">
         <v>13</v>
@@ -2740,11 +2750,11 @@
       <c r="D23" s="12">
         <v>3</v>
       </c>
-      <c r="E23" s="13">
-        <v>46315</v>
-      </c>
-      <c r="F23" s="13">
-        <v>46331</v>
+      <c r="E23" s="25">
+        <v>46332</v>
+      </c>
+      <c r="F23" s="25">
+        <v>46350</v>
       </c>
       <c r="G23" s="10">
         <v>13</v>
@@ -2766,11 +2776,11 @@
       <c r="D24" s="12">
         <v>2</v>
       </c>
-      <c r="E24" s="13">
-        <v>46332</v>
-      </c>
-      <c r="F24" s="13">
-        <v>46344</v>
+      <c r="E24" s="25">
+        <v>46351</v>
+      </c>
+      <c r="F24" s="25">
+        <v>46363</v>
       </c>
       <c r="G24" s="10">
         <v>9</v>
@@ -2792,11 +2802,11 @@
       <c r="D25" s="12">
         <v>2</v>
       </c>
-      <c r="E25" s="13">
-        <v>46345</v>
-      </c>
-      <c r="F25" s="13">
-        <v>46356</v>
+      <c r="E25" s="25">
+        <v>46364</v>
+      </c>
+      <c r="F25" s="25">
+        <v>46373</v>
       </c>
       <c r="G25" s="10">
         <v>8</v>
@@ -2805,25 +2815,25 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="28.8">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15" t="s">
+    <row r="26" spans="1:8" ht="28.8" customHeight="1">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>36</v>
       </c>
-      <c r="E26" s="16">
-        <v>46225</v>
-      </c>
-      <c r="F26" s="16">
-        <v>46356</v>
-      </c>
-      <c r="G26" s="14">
+      <c r="E26" s="26">
+        <v>46244</v>
+      </c>
+      <c r="F26" s="26">
+        <v>46373</v>
+      </c>
+      <c r="G26" s="13">
         <v>92</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="16" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2838,242 +2848,242 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="18" style="24" customWidth="1"/>
+    <col min="2" max="5" width="14" style="24" customWidth="1"/>
+    <col min="6" max="6" width="18" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:6" ht="18" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>11</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>24</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>46225</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <v>46295</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="18">
         <v>24</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>36</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="27">
+        <v>46244</v>
+      </c>
+      <c r="E6" s="27">
+        <v>46373</v>
+      </c>
+      <c r="F6" s="18">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="20">
+        <v>35</v>
+      </c>
+      <c r="C7" s="20">
+        <v>60</v>
+      </c>
+      <c r="D7" s="28">
         <v>46225</v>
       </c>
-      <c r="E6" s="20">
-        <v>46356</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E7" s="28">
+        <v>46373</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="21">
-        <v>35</v>
-      </c>
-      <c r="C7" s="21">
-        <v>60</v>
-      </c>
-      <c r="D7" s="22">
-        <v>46225</v>
-      </c>
-      <c r="E7" s="22">
-        <v>46356</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="24">
+      <c r="A11" s="22">
         <v>46251</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="24">
+      <c r="A12" s="22">
         <v>46259</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="23" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.05" customHeight="1">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/docs/bobot_kesulitan_modul_fprs_v3.xlsx
+++ b/docs/bobot_kesulitan_modul_fprs_v3.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Semua Modul" sheetId="1" r:id="rId1"/>
